--- a/data/trans_dic/P12_2_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P12_2_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que refirió mucha energía alguna vez o algunas veces</t>
+          <t>Población que refirió mucha energía alguna vez o algunas veces (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,56; 20,83</t>
+          <t>13,52; 20,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,83; 19,22</t>
+          <t>12,24; 18,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,32; 16,83</t>
+          <t>10,28; 16,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,1; 19,25</t>
+          <t>13,02; 19,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>21,6; 31,36</t>
+          <t>21,3; 31,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,66; 26,13</t>
+          <t>16,33; 26,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,86; 17,65</t>
+          <t>10,27; 18,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,73; 21,0</t>
+          <t>14,61; 20,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,12; 24,02</t>
+          <t>18,09; 23,47</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,9; 20,54</t>
+          <t>14,56; 20,58</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,93; 16,11</t>
+          <t>10,85; 16,24</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,7; 19,13</t>
+          <t>14,6; 19,3</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,57; 20,6</t>
+          <t>12,65; 20,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,26; 21,07</t>
+          <t>12,93; 20,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,77; 11,72</t>
+          <t>5,44; 11,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,59; 17,04</t>
+          <t>10,65; 16,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,54; 29,4</t>
+          <t>20,62; 29,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,06; 27,35</t>
+          <t>18,03; 27,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,33; 21,96</t>
+          <t>13,31; 21,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,95; 24,96</t>
+          <t>18,19; 25,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,56; 23,87</t>
+          <t>17,62; 23,77</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16,22; 22,49</t>
+          <t>15,97; 22,38</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,28; 15,37</t>
+          <t>10,37; 15,64</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,9; 19,68</t>
+          <t>14,98; 19,76</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,29; 23,34</t>
+          <t>16,5; 23,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,24; 22,89</t>
+          <t>16,39; 22,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,48; 21,2</t>
+          <t>14,23; 21,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,64; 18,37</t>
+          <t>4,53; 18,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,22; 36,0</t>
+          <t>22,01; 35,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,61; 29,25</t>
+          <t>18,63; 29,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,87; 28,99</t>
+          <t>15,67; 29,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20,81; 32,27</t>
+          <t>21,13; 32,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,68; 24,62</t>
+          <t>18,76; 24,84</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,16; 23,47</t>
+          <t>18,17; 23,62</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,87; 22,13</t>
+          <t>15,74; 21,89</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,81; 20,63</t>
+          <t>6,51; 20,7</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,37; 26,25</t>
+          <t>21,48; 26,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,08; 21,74</t>
+          <t>16,92; 21,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,47; 19,88</t>
+          <t>15,37; 19,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,96; 21,9</t>
+          <t>16,89; 21,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,33; 27,6</t>
+          <t>21,54; 27,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,29; 24,72</t>
+          <t>18,46; 24,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,15; 20,69</t>
+          <t>15,61; 21,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,84; 22,72</t>
+          <t>10,21; 23,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22,1; 25,94</t>
+          <t>22,22; 26,31</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,36; 22,17</t>
+          <t>18,26; 21,98</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16,01; 19,64</t>
+          <t>16,22; 19,6</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,19; 21,27</t>
+          <t>12,11; 20,95</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,75; 26,41</t>
+          <t>17,21; 26,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,24; 21,36</t>
+          <t>14,46; 21,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,38; 23,99</t>
+          <t>17,71; 24,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,87; 25,59</t>
+          <t>17,53; 25,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>28,63; 36,55</t>
+          <t>28,75; 36,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,34; 34,31</t>
+          <t>27,14; 34,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,66; 32,51</t>
+          <t>25,64; 32,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,85; 29,26</t>
+          <t>18,96; 29,21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>25,13; 31,16</t>
+          <t>25,42; 31,53</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23,1; 28,1</t>
+          <t>23,03; 28,07</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22,71; 27,36</t>
+          <t>22,94; 27,43</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,44; 26,6</t>
+          <t>19,41; 26,42</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,58; 10,4</t>
+          <t>4,57; 10,44</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,45; 11,11</t>
+          <t>4,51; 11,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,58; 10,83</t>
+          <t>4,8; 11,04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,27; 11,5</t>
+          <t>2,19; 10,66</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>31,21; 36,7</t>
+          <t>31,08; 36,37</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,53; 30,09</t>
+          <t>24,73; 30,46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,74; 28,48</t>
+          <t>22,73; 27,95</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20,36; 25,36</t>
+          <t>20,41; 25,33</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26,41; 30,94</t>
+          <t>26,28; 30,91</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21,22; 25,82</t>
+          <t>21,05; 25,85</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19,33; 23,8</t>
+          <t>19,43; 23,92</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16,25; 20,84</t>
+          <t>16,19; 20,88</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>18,23; 21,05</t>
+          <t>18,21; 21,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,93; 18,8</t>
+          <t>15,96; 18,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14,47; 16,89</t>
+          <t>14,45; 16,92</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,07; 17,38</t>
+          <t>11,99; 17,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>28,2; 31,38</t>
+          <t>28,07; 31,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,87; 26,89</t>
+          <t>23,8; 26,99</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,77; 23,7</t>
+          <t>20,78; 23,67</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>17,14; 23,31</t>
+          <t>17,03; 23,37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>23,63; 25,74</t>
+          <t>23,66; 25,68</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20,52; 22,46</t>
+          <t>20,44; 22,5</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18,01; 19,86</t>
+          <t>18,04; 19,92</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>16,15; 20,12</t>
+          <t>16,01; 19,98</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que refirió mucha energía alguna vez o algunas veces</t>
+          <t>Población que refirió mucha energía alguna vez o algunas veces (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>64265; 98707</t>
+          <t>64035; 98289</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>51708; 84022</t>
+          <t>53502; 83001</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44293; 72207</t>
+          <t>44116; 70976</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>66178; 97238</t>
+          <t>65762; 98730</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>66240; 96173</t>
+          <t>65336; 96567</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>52380; 82151</t>
+          <t>51349; 82061</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34212; 61254</t>
+          <t>35629; 63038</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>65894; 93950</t>
+          <t>65362; 91483</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>141400; 187445</t>
+          <t>141171; 183173</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>111981; 154382</t>
+          <t>109480; 154683</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>84851; 125028</t>
+          <t>84229; 126060</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>140088; 182228</t>
+          <t>139076; 183887</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>46108; 75604</t>
+          <t>46435; 75492</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>55531; 88247</t>
+          <t>54145; 87504</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21703; 44110</t>
+          <t>20488; 41676</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>47904; 77055</t>
+          <t>48180; 76647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>76390; 109340</t>
+          <t>76688; 110329</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>61047; 92450</t>
+          <t>60947; 93971</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>49473; 81524</t>
+          <t>49398; 81326</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>68673; 95487</t>
+          <t>69594; 95712</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>129705; 176322</t>
+          <t>130206; 175624</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>122727; 170219</t>
+          <t>120836; 169368</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>76875; 114917</t>
+          <t>77481; 116913</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>124383; 164317</t>
+          <t>125047; 164963</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>88371; 126600</t>
+          <t>89485; 125194</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>102010; 143800</t>
+          <t>102960; 142374</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>75384; 110422</t>
+          <t>74087; 112526</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24351; 122770</t>
+          <t>30252; 125217</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>37286; 60398</t>
+          <t>36931; 60087</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>48236; 75783</t>
+          <t>48275; 75998</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24704; 48152</t>
+          <t>26029; 48575</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>34622; 53673</t>
+          <t>35144; 53673</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>132686; 174858</t>
+          <t>133194; 176440</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>161135; 208233</t>
+          <t>161285; 209640</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>109017; 152030</t>
+          <t>108082; 150344</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>48483; 172169</t>
+          <t>54301; 172745</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>264656; 325021</t>
+          <t>266036; 322872</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>197796; 251816</t>
+          <t>195965; 254205</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>177494; 228154</t>
+          <t>176392; 228562</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>175390; 226370</t>
+          <t>174644; 224371</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>152350; 197133</t>
+          <t>153854; 198975</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>139839; 188990</t>
+          <t>141135; 185422</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>124847; 170512</t>
+          <t>128594; 173171</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>86459; 222265</t>
+          <t>99888; 226513</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>431572; 506523</t>
+          <t>433936; 513687</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>352912; 426258</t>
+          <t>351036; 422556</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>315641; 387321</t>
+          <t>319746; 386469</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>265288; 427915</t>
+          <t>243639; 421416</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>62210; 92585</t>
+          <t>60339; 91469</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>72700; 109052</t>
+          <t>73824; 107684</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>107902; 148918</t>
+          <t>109931; 150404</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>84881; 121588</t>
+          <t>83262; 118793</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>162844; 207862</t>
+          <t>163501; 208587</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>207976; 260968</t>
+          <t>206420; 259947</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>189470; 240020</t>
+          <t>189318; 238177</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>158434; 245905</t>
+          <t>159293; 245413</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>230988; 286427</t>
+          <t>233652; 289868</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>293637; 357198</t>
+          <t>292780; 356773</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>308609; 371859</t>
+          <t>311786; 372783</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>255677; 349932</t>
+          <t>255358; 347550</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>13652; 31009</t>
+          <t>13641; 31118</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11846; 29550</t>
+          <t>11991; 31290</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13138; 31091</t>
+          <t>13792; 31705</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5453; 27652</t>
+          <t>5276; 25645</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>389707; 458252</t>
+          <t>388166; 454230</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>271411; 332880</t>
+          <t>273583; 336958</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>245322; 307263</t>
+          <t>245213; 301456</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>154640; 192583</t>
+          <t>154960; 192324</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>408606; 478646</t>
+          <t>406545; 478139</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>291223; 354355</t>
+          <t>288901; 354684</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>264031; 325081</t>
+          <t>265435; 326680</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>162458; 208414</t>
+          <t>161864; 208807</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>596270; 688309</t>
+          <t>595543; 686770</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>544583; 642581</t>
+          <t>545491; 642688</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>489155; 571031</t>
+          <t>488524; 572036</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>407443; 586469</t>
+          <t>404704; 586816</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>952715; 1060053</t>
+          <t>948349; 1058473</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>845875; 952726</t>
+          <t>843428; 956310</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>732176; 835477</t>
+          <t>732630; 834350</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>612495; 833104</t>
+          <t>608721; 835178</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1571295; 1711058</t>
+          <t>1573275; 1707153</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1428629; 1563961</t>
+          <t>1423331; 1566348</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1244148; 1371708</t>
+          <t>1245924; 1375721</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1122388; 1398319</t>
+          <t>1112440; 1388757</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P12_2_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P12_2_R-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,07%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,52; 20,75</t>
+          <t>13,9; 20,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,24; 18,98</t>
+          <t>11,97; 19,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,28; 16,54</t>
+          <t>10,01; 16,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,02; 19,54</t>
+          <t>13,28; 19,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>21,3; 31,49</t>
+          <t>20,88; 31,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,33; 26,1</t>
+          <t>16,23; 25,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,27; 18,16</t>
+          <t>10,05; 17,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,61; 20,44</t>
+          <t>15,12; 21,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,09; 23,47</t>
+          <t>17,86; 23,58</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,56; 20,58</t>
+          <t>14,98; 20,84</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,85; 16,24</t>
+          <t>11,02; 16,05</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,6; 19,3</t>
+          <t>15,02; 19,52</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,17%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,65; 20,57</t>
+          <t>12,57; 20,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,93; 20,89</t>
+          <t>13,06; 21,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,44; 11,08</t>
+          <t>5,69; 11,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,65; 16,95</t>
+          <t>10,76; 17,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,62; 29,67</t>
+          <t>20,66; 29,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,03; 27,8</t>
+          <t>17,71; 27,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,31; 21,91</t>
+          <t>13,24; 21,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,19; 25,02</t>
+          <t>18,28; 24,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,62; 23,77</t>
+          <t>17,86; 24,17</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15,97; 22,38</t>
+          <t>16,18; 22,63</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,37; 15,64</t>
+          <t>10,18; 15,12</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,98; 19,76</t>
+          <t>15,06; 19,8</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>19,64%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,5; 23,08</t>
+          <t>16,63; 23,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,39; 22,66</t>
+          <t>16,37; 22,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,23; 21,61</t>
+          <t>14,53; 21,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,53; 18,74</t>
+          <t>13,79; 20,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,01; 35,81</t>
+          <t>21,91; 35,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,63; 29,33</t>
+          <t>18,48; 29,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,67; 29,24</t>
+          <t>14,79; 28,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21,13; 32,27</t>
+          <t>20,6; 31,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,76; 24,84</t>
+          <t>18,98; 24,93</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,17; 23,62</t>
+          <t>17,96; 23,49</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,74; 21,89</t>
+          <t>15,64; 21,82</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,51; 20,7</t>
+          <t>16,98; 22,66</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>20,74%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,48; 26,07</t>
+          <t>21,13; 25,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,92; 21,95</t>
+          <t>16,86; 21,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,37; 19,92</t>
+          <t>15,48; 19,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,89; 21,7</t>
+          <t>16,83; 21,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,54; 27,86</t>
+          <t>21,02; 27,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,46; 24,25</t>
+          <t>18,2; 24,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,61; 21,01</t>
+          <t>15,61; 20,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,21; 23,16</t>
+          <t>20,93; 25,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22,22; 26,31</t>
+          <t>22,15; 25,93</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,26; 21,98</t>
+          <t>18,14; 21,81</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16,22; 19,6</t>
+          <t>16,19; 19,65</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,11; 20,95</t>
+          <t>18,88; 22,39</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,9%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,21; 26,09</t>
+          <t>17,38; 26,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,46; 21,09</t>
+          <t>14,51; 21,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,71; 24,23</t>
+          <t>17,65; 24,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,53; 25,01</t>
+          <t>17,14; 24,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>28,75; 36,67</t>
+          <t>28,56; 36,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,14; 34,18</t>
+          <t>27,43; 34,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,64; 32,26</t>
+          <t>25,54; 32,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,96; 29,21</t>
+          <t>25,11; 30,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>25,42; 31,53</t>
+          <t>25,24; 31,3</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23,03; 28,07</t>
+          <t>23,07; 28,11</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22,94; 27,43</t>
+          <t>22,74; 27,24</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,41; 26,42</t>
+          <t>22,78; 26,79</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,83%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,57; 10,44</t>
+          <t>4,41; 10,76</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,51; 11,77</t>
+          <t>4,56; 11,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,8; 11,04</t>
+          <t>4,51; 11,09</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,19; 10,66</t>
+          <t>2,55; 11,2</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>31,08; 36,37</t>
+          <t>31,43; 36,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,73; 30,46</t>
+          <t>24,54; 30,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,73; 27,95</t>
+          <t>22,4; 28,09</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20,41; 25,33</t>
+          <t>20,18; 25,26</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26,28; 30,91</t>
+          <t>26,39; 30,95</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21,05; 25,85</t>
+          <t>21,22; 25,92</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19,43; 23,92</t>
+          <t>19,35; 23,69</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16,19; 20,88</t>
+          <t>16,82; 21,43</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>20,17%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>18,21; 21,0</t>
+          <t>18,11; 20,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,96; 18,8</t>
+          <t>15,98; 18,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14,45; 16,92</t>
+          <t>14,31; 16,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,99; 17,39</t>
+          <t>15,49; 18,19</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>28,07; 31,33</t>
+          <t>28,19; 31,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,8; 26,99</t>
+          <t>23,84; 27,07</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,78; 23,67</t>
+          <t>20,72; 23,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>17,03; 23,37</t>
+          <t>22,22; 24,58</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>23,66; 25,68</t>
+          <t>23,55; 25,69</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20,44; 22,5</t>
+          <t>20,48; 22,5</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18,04; 19,92</t>
+          <t>18,03; 19,96</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>16,01; 19,98</t>
+          <t>19,27; 21,01</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>81331</t>
+          <t>88218</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>79093</t>
+          <t>89195</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>160424</t>
+          <t>177413</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>64035; 98289</t>
+          <t>65847; 98846</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>53502; 83001</t>
+          <t>52342; 83522</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44116; 70976</t>
+          <t>42969; 71390</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>65762; 98730</t>
+          <t>73096; 108419</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>65336; 96567</t>
+          <t>64020; 96883</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>51349; 82061</t>
+          <t>51042; 80363</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35629; 63038</t>
+          <t>34893; 61085</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>65362; 91483</t>
+          <t>73848; 104470</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>141171; 183173</t>
+          <t>139400; 184030</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>109480; 154683</t>
+          <t>112627; 156672</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>84229; 126060</t>
+          <t>85521; 124600</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>139076; 183887</t>
+          <t>156044; 202804</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>61986</t>
+          <t>65305</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>81916</t>
+          <t>90331</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>143902</t>
+          <t>155636</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>46435; 75492</t>
+          <t>46124; 76674</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>54145; 87504</t>
+          <t>54713; 88936</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20488; 41676</t>
+          <t>21422; 44425</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>48180; 76647</t>
+          <t>52014; 82610</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>76688; 110329</t>
+          <t>76831; 110280</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>60947; 93971</t>
+          <t>59858; 91889</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>49398; 81326</t>
+          <t>49159; 80630</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>69594; 95712</t>
+          <t>77338; 104291</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>130206; 175624</t>
+          <t>131959; 178565</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>120836; 169368</t>
+          <t>122423; 171249</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>77481; 116913</t>
+          <t>76083; 113017</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>125047; 164963</t>
+          <t>136460; 179435</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>73115</t>
+          <t>81319</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>43615</t>
+          <t>48018</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>116730</t>
+          <t>129337</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>89485; 125194</t>
+          <t>90222; 126753</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>102960; 142374</t>
+          <t>102869; 143714</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>74087; 112526</t>
+          <t>75649; 112719</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30252; 125217</t>
+          <t>65026; 95745</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>36931; 60087</t>
+          <t>36754; 60066</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>48275; 75998</t>
+          <t>47878; 75549</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26029; 48575</t>
+          <t>24566; 47642</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>35144; 53673</t>
+          <t>38515; 58408</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>133194; 176440</t>
+          <t>134773; 177052</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>161285; 209640</t>
+          <t>159382; 208492</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>108082; 150344</t>
+          <t>107461; 149887</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>54301; 172745</t>
+          <t>111841; 149235</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>199306</t>
+          <t>214903</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>171398</t>
+          <t>198305</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>370704</t>
+          <t>413208</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>266036; 322872</t>
+          <t>261623; 321608</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>195965; 254205</t>
+          <t>195207; 251488</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>176392; 228562</t>
+          <t>177702; 228451</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>174644; 224371</t>
+          <t>190349; 241725</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>153854; 198975</t>
+          <t>150128; 196780</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>141135; 185422</t>
+          <t>139124; 187260</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>128594; 173171</t>
+          <t>128608; 172243</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>99888; 226513</t>
+          <t>180255; 219497</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>433936; 513687</t>
+          <t>432581; 506366</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>351036; 422556</t>
+          <t>348836; 419422</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>319746; 386469</t>
+          <t>319121; 387489</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>243639; 421416</t>
+          <t>376189; 446020</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>101045</t>
+          <t>115662</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>213784</t>
+          <t>232316</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>314829</t>
+          <t>347978</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>60339; 91469</t>
+          <t>60935; 91808</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>73824; 107684</t>
+          <t>74090; 107932</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>109931; 150404</t>
+          <t>109564; 149399</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>83262; 118793</t>
+          <t>97331; 137967</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>163501; 208587</t>
+          <t>162444; 208409</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>206420; 259947</t>
+          <t>208616; 261782</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>189318; 238177</t>
+          <t>188542; 239528</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>159293; 245413</t>
+          <t>208381; 253926</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>233652; 289868</t>
+          <t>232045; 287783</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>292780; 356773</t>
+          <t>293199; 357291</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>311786; 372783</t>
+          <t>309043; 370169</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>255358; 347550</t>
+          <t>318436; 374400</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11829</t>
+          <t>12856</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>172974</t>
+          <t>190412</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>184802</t>
+          <t>203268</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>13641; 31118</t>
+          <t>13152; 32074</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11991; 31290</t>
+          <t>12119; 30514</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13792; 31705</t>
+          <t>12949; 31841</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5276; 25645</t>
+          <t>6049; 26563</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>388166; 454230</t>
+          <t>392429; 455589</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>273583; 336958</t>
+          <t>271561; 334406</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>245213; 301456</t>
+          <t>241665; 302975</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>154960; 192324</t>
+          <t>169995; 212760</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>406545; 478139</t>
+          <t>408255; 478772</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>288901; 354684</t>
+          <t>291191; 355697</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>265435; 326680</t>
+          <t>264269; 323566</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>161864; 208807</t>
+          <t>181604; 231355</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>528612</t>
+          <t>578263</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>762779</t>
+          <t>848577</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1291391</t>
+          <t>1426840</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>595543; 686770</t>
+          <t>592124; 683170</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>545491; 642688</t>
+          <t>546401; 635939</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>488524; 572036</t>
+          <t>483772; 568031</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>404704; 586816</t>
+          <t>532920; 625849</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>948349; 1058473</t>
+          <t>952375; 1057751</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>843428; 956310</t>
+          <t>844587; 959162</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>732630; 834350</t>
+          <t>730499; 830539</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>608721; 835178</t>
+          <t>806844; 892616</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1573275; 1707153</t>
+          <t>1565602; 1708049</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1423331; 1566348</t>
+          <t>1425895; 1566196</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1245924; 1375721</t>
+          <t>1245193; 1378379</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1112440; 1388757</t>
+          <t>1362808; 1486194</t>
         </is>
       </c>
     </row>
